--- a/public/assets/media/svg/files/product.xlsx
+++ b/public/assets/media/svg/files/product.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Arabic_Name</t>
   </si>
@@ -72,9 +72,6 @@
     <t>SubCategory</t>
   </si>
   <si>
-    <t>فروج مشوي</t>
-  </si>
-  <si>
     <t>وجبة</t>
   </si>
   <si>
@@ -90,10 +87,28 @@
     <t>سندويش</t>
   </si>
   <si>
-    <t>Fried Chicken11</t>
-  </si>
-  <si>
     <t>Price_with_tax</t>
+  </si>
+  <si>
+    <t>Establishment</t>
+  </si>
+  <si>
+    <t>فروج مشوي 1</t>
+  </si>
+  <si>
+    <t>جميع المستودعات</t>
+  </si>
+  <si>
+    <t>Fried Chicken1</t>
+  </si>
+  <si>
+    <t>Fried Chicken2</t>
+  </si>
+  <si>
+    <t>فروج مشوي 2</t>
+  </si>
+  <si>
+    <t>مستودع الرياض المركزي</t>
   </si>
 </sst>
 </file>
@@ -459,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -472,7 +487,7 @@
     <col min="16" max="16" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,21 +528,24 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -536,10 +554,10 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
         <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -554,10 +572,54 @@
         <v>15</v>
       </c>
       <c r="O2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <v>12</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
